--- a/Dashboard_GIS/ข้อมูลดิบ/แรงดันน้ำ/PRESSURE_ตราด_ปีงบ69.xlsx
+++ b/Dashboard_GIS/ข้อมูลดิบ/แรงดันน้ำ/PRESSURE_ตราด_ปีงบ69.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Report" sheetId="1" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="false" name="__bookmark_1" vbProcedure="false">Report!$A$4:$M$106</definedName>
+    <definedName function="false" hidden="false" name="__bookmark_1" vbProcedure="false">Report!$A$4:$N$106</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="123">
   <si>
     <t xml:space="preserve">รายงานการตรวจวัดค่าแรงดันน้ำ</t>
   </si>
@@ -322,6 +322,48 @@
         <family val="2"/>
         <charset val="222"/>
       </rPr>
+      <t xml:space="preserve">เม</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="222"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="222"/>
+      </rPr>
+      <t xml:space="preserve">ย</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="222"/>
+      </rPr>
+      <t xml:space="preserve">. 69</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="222"/>
+      </rPr>
       <t xml:space="preserve">ก</t>
     </r>
     <r>
@@ -2084,7 +2126,7 @@
     <t xml:space="preserve">พิมพ์รายงานวันที่</t>
   </si>
   <si>
-    <t xml:space="preserve">4/3/2569</t>
+    <t xml:space="preserve">3/4/2569</t>
   </si>
   <si>
     <t xml:space="preserve">หน้าที่</t>
@@ -2297,7 +2339,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:V111"/>
+  <dimension ref="A1:W111"/>
   <sheetFormatPr defaultColWidth="11.74609375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4.6"/>
@@ -2311,15 +2353,16 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="3.33"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="6.6"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="6.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="23.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="9.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="1.6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="5.69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="7.03"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="1.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="5.22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="0.6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="2.7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="6.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="17.02"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="9.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="1.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="5.69"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="7.03"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="1.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="5.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="0.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="0" width="2.7"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2341,11 +2384,12 @@
       <c r="N1" s="2"/>
       <c r="O1" s="2"/>
       <c r="P1" s="2"/>
-      <c r="Q1" s="3"/>
+      <c r="Q1" s="2"/>
       <c r="R1" s="3"/>
       <c r="S1" s="3"/>
       <c r="T1" s="3"/>
       <c r="U1" s="3"/>
+      <c r="V1" s="3"/>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1"/>
@@ -2366,11 +2410,12 @@
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
       <c r="P2" s="2"/>
-      <c r="Q2" s="3"/>
+      <c r="Q2" s="2"/>
       <c r="R2" s="3"/>
       <c r="S2" s="3"/>
       <c r="T2" s="3"/>
       <c r="U2" s="3"/>
+      <c r="V2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1"/>
@@ -2391,11 +2436,12 @@
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
       <c r="P3" s="2"/>
-      <c r="Q3" s="3"/>
+      <c r="Q3" s="2"/>
       <c r="R3" s="3"/>
       <c r="S3" s="3"/>
       <c r="T3" s="3"/>
       <c r="U3" s="3"/>
+      <c r="V3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4"/>
@@ -2411,6 +2457,7 @@
       <c r="K4" s="4"/>
       <c r="L4" s="4"/>
       <c r="M4" s="4"/>
+      <c r="N4" s="4"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
@@ -2445,6 +2492,9 @@
       </c>
       <c r="M5" s="5" t="s">
         <v>12</v>
+      </c>
+      <c r="N5" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2461,18 +2511,19 @@
       <c r="K6" s="6"/>
       <c r="L6" s="6"/>
       <c r="M6" s="6"/>
+      <c r="N6" s="6"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="n">
         <v>1</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
       <c r="E7" s="7" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="F7" s="9" t="n">
         <v>2.5</v>
@@ -2491,9 +2542,12 @@
       </c>
       <c r="K7" s="9"/>
       <c r="L7" s="9" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M7" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2502,12 +2556,12 @@
         <v>2</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C8" s="8"/>
       <c r="D8" s="8"/>
       <c r="E8" s="7" t="n">
-        <v>2.7</v>
+        <v>2.683333</v>
       </c>
       <c r="F8" s="9" t="n">
         <v>2.7</v>
@@ -2526,9 +2580,12 @@
       </c>
       <c r="K8" s="9"/>
       <c r="L8" s="9" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2537,12 +2594,12 @@
         <v>3</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" s="8"/>
       <c r="D9" s="8"/>
       <c r="E9" s="7" t="n">
-        <v>1.92</v>
+        <v>1.933333</v>
       </c>
       <c r="F9" s="9" t="n">
         <v>1.9</v>
@@ -2561,9 +2618,12 @@
       </c>
       <c r="K9" s="9"/>
       <c r="L9" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2572,12 +2632,12 @@
         <v>4</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
       <c r="E10" s="7" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="F10" s="9" t="n">
         <v>1.2</v>
@@ -2596,9 +2656,12 @@
       </c>
       <c r="K10" s="9"/>
       <c r="L10" s="9" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="M10" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2607,12 +2670,12 @@
         <v>5</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C11" s="8"/>
       <c r="D11" s="8"/>
       <c r="E11" s="7" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="F11" s="9" t="n">
         <v>1.6</v>
@@ -2631,9 +2694,12 @@
       </c>
       <c r="K11" s="9"/>
       <c r="L11" s="9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2642,12 +2708,12 @@
         <v>6</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C12" s="8"/>
       <c r="D12" s="8"/>
       <c r="E12" s="7" t="n">
-        <v>1.16</v>
+        <v>1.133333</v>
       </c>
       <c r="F12" s="9" t="n">
         <v>1.2</v>
@@ -2666,9 +2732,12 @@
       </c>
       <c r="K12" s="9"/>
       <c r="L12" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2677,12 +2746,12 @@
         <v>7</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C13" s="8"/>
       <c r="D13" s="8"/>
       <c r="E13" s="7" t="n">
-        <v>2</v>
+        <v>1.983333</v>
       </c>
       <c r="F13" s="9" t="n">
         <v>2</v>
@@ -2701,9 +2770,12 @@
       </c>
       <c r="K13" s="9"/>
       <c r="L13" s="9" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M13" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2712,12 +2784,12 @@
         <v>8</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C14" s="8"/>
       <c r="D14" s="8"/>
       <c r="E14" s="7" t="n">
-        <v>1.47</v>
+        <v>1.475</v>
       </c>
       <c r="F14" s="9" t="n">
         <v>1.5</v>
@@ -2736,9 +2808,12 @@
       </c>
       <c r="K14" s="9"/>
       <c r="L14" s="9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2747,12 +2822,12 @@
         <v>9</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C15" s="8"/>
       <c r="D15" s="8"/>
       <c r="E15" s="7" t="n">
-        <v>1.66</v>
+        <v>1.666666</v>
       </c>
       <c r="F15" s="9" t="n">
         <v>1.5</v>
@@ -2771,9 +2846,12 @@
       </c>
       <c r="K15" s="9"/>
       <c r="L15" s="9" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2782,12 +2860,12 @@
         <v>10</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
       <c r="E16" s="7" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="F16" s="9" t="n">
         <v>1</v>
@@ -2806,9 +2884,12 @@
       </c>
       <c r="K16" s="9"/>
       <c r="L16" s="9" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="M16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2817,12 +2898,12 @@
         <v>11</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
       <c r="E17" s="7" t="n">
-        <v>1.62</v>
+        <v>1.633333</v>
       </c>
       <c r="F17" s="9" t="n">
         <v>1.5</v>
@@ -2841,9 +2922,12 @@
       </c>
       <c r="K17" s="9"/>
       <c r="L17" s="9" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2852,12 +2936,12 @@
         <v>12</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C18" s="8"/>
       <c r="D18" s="8"/>
       <c r="E18" s="7" t="n">
-        <v>2.926</v>
+        <v>2.921666</v>
       </c>
       <c r="F18" s="9" t="n">
         <v>2.85</v>
@@ -2876,9 +2960,12 @@
       </c>
       <c r="K18" s="9"/>
       <c r="L18" s="9" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2887,12 +2974,12 @@
         <v>13</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C19" s="8"/>
       <c r="D19" s="8"/>
       <c r="E19" s="7" t="n">
-        <v>2.466</v>
+        <v>2.471666</v>
       </c>
       <c r="F19" s="9" t="n">
         <v>2.46</v>
@@ -2911,9 +2998,12 @@
       </c>
       <c r="K19" s="9"/>
       <c r="L19" s="9" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M19" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2922,12 +3012,12 @@
         <v>14</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C20" s="8"/>
       <c r="D20" s="8"/>
       <c r="E20" s="7" t="n">
-        <v>2.39</v>
+        <v>2.375</v>
       </c>
       <c r="F20" s="9" t="n">
         <v>2.4</v>
@@ -2946,9 +3036,12 @@
       </c>
       <c r="K20" s="9"/>
       <c r="L20" s="9" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M20" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2957,12 +3050,12 @@
         <v>15</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
       <c r="E21" s="7" t="n">
-        <v>1.64</v>
+        <v>1.633333</v>
       </c>
       <c r="F21" s="9" t="n">
         <v>1.6</v>
@@ -2981,9 +3074,12 @@
       </c>
       <c r="K21" s="9"/>
       <c r="L21" s="9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M21" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2992,12 +3088,12 @@
         <v>16</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
       <c r="E22" s="7" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="F22" s="9" t="n">
         <v>0.8</v>
@@ -3016,9 +3112,12 @@
       </c>
       <c r="K22" s="9"/>
       <c r="L22" s="9" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="M22" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3027,12 +3126,12 @@
         <v>17</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
       <c r="E23" s="7" t="n">
-        <v>2.116</v>
+        <v>2.113333</v>
       </c>
       <c r="F23" s="9" t="n">
         <v>1.96</v>
@@ -3051,9 +3150,12 @@
       </c>
       <c r="K23" s="9"/>
       <c r="L23" s="9" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M23" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3062,12 +3164,12 @@
         <v>18</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
       <c r="E24" s="7" t="n">
-        <v>1.56</v>
+        <v>1.566666</v>
       </c>
       <c r="F24" s="9" t="n">
         <v>1.6</v>
@@ -3086,9 +3188,12 @@
       </c>
       <c r="K24" s="9"/>
       <c r="L24" s="9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3097,12 +3202,12 @@
         <v>19</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
       <c r="E25" s="7" t="n">
-        <v>2.08</v>
+        <v>2.083333</v>
       </c>
       <c r="F25" s="9" t="n">
         <v>2.2</v>
@@ -3121,9 +3226,12 @@
       </c>
       <c r="K25" s="9"/>
       <c r="L25" s="9" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M25" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3132,12 +3240,12 @@
         <v>20</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C26" s="8"/>
       <c r="D26" s="8"/>
       <c r="E26" s="7" t="n">
-        <v>2.132</v>
+        <v>2.126666</v>
       </c>
       <c r="F26" s="9" t="n">
         <v>2.1</v>
@@ -3156,9 +3264,12 @@
       </c>
       <c r="K26" s="9"/>
       <c r="L26" s="9" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M26" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3167,7 +3278,7 @@
         <v>21</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>
@@ -3191,9 +3302,12 @@
       </c>
       <c r="K27" s="9"/>
       <c r="L27" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M27" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3202,12 +3316,12 @@
         <v>22</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
       <c r="E28" s="7" t="n">
-        <v>2</v>
+        <v>2.016666</v>
       </c>
       <c r="F28" s="9" t="n">
         <v>2</v>
@@ -3226,9 +3340,12 @@
       </c>
       <c r="K28" s="9"/>
       <c r="L28" s="9" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M28" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3237,12 +3354,12 @@
         <v>23</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C29" s="8"/>
       <c r="D29" s="8"/>
       <c r="E29" s="7" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="F29" s="9" t="n">
         <v>1.5</v>
@@ -3261,9 +3378,12 @@
       </c>
       <c r="K29" s="9"/>
       <c r="L29" s="9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M29" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3272,12 +3392,12 @@
         <v>24</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
       <c r="E30" s="7" t="n">
-        <v>1.48</v>
+        <v>1.483333</v>
       </c>
       <c r="F30" s="9" t="n">
         <v>1.4</v>
@@ -3296,9 +3416,12 @@
       </c>
       <c r="K30" s="9"/>
       <c r="L30" s="9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M30" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3307,12 +3430,12 @@
         <v>25</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C31" s="8"/>
       <c r="D31" s="8"/>
       <c r="E31" s="7" t="n">
-        <v>1.42</v>
+        <v>1.433333</v>
       </c>
       <c r="F31" s="9" t="n">
         <v>1.3</v>
@@ -3331,9 +3454,12 @@
       </c>
       <c r="K31" s="9"/>
       <c r="L31" s="9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M31" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3342,12 +3468,12 @@
         <v>26</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C32" s="8"/>
       <c r="D32" s="8"/>
       <c r="E32" s="7" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="F32" s="9" t="n">
         <v>1.9</v>
@@ -3366,9 +3492,12 @@
       </c>
       <c r="K32" s="9"/>
       <c r="L32" s="9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M32" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3377,12 +3506,12 @@
         <v>27</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C33" s="8"/>
       <c r="D33" s="8"/>
       <c r="E33" s="7" t="n">
-        <v>1.84</v>
+        <v>1.833333</v>
       </c>
       <c r="F33" s="9" t="n">
         <v>1.8</v>
@@ -3401,9 +3530,12 @@
       </c>
       <c r="K33" s="9"/>
       <c r="L33" s="9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M33" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3412,12 +3544,12 @@
         <v>28</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C34" s="8"/>
       <c r="D34" s="8"/>
       <c r="E34" s="7" t="n">
-        <v>1.028</v>
+        <v>1.14</v>
       </c>
       <c r="F34" s="9" t="n">
         <v>1</v>
@@ -3436,9 +3568,12 @@
       </c>
       <c r="K34" s="9"/>
       <c r="L34" s="9" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M34" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3447,12 +3582,12 @@
         <v>29</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C35" s="8"/>
       <c r="D35" s="8"/>
       <c r="E35" s="7" t="n">
-        <v>2.362</v>
+        <v>2.401666</v>
       </c>
       <c r="F35" s="9" t="n">
         <v>2.7</v>
@@ -3471,9 +3606,12 @@
       </c>
       <c r="K35" s="9"/>
       <c r="L35" s="9" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M35" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3482,12 +3620,12 @@
         <v>30</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C36" s="8"/>
       <c r="D36" s="8"/>
       <c r="E36" s="7" t="n">
-        <v>2.32</v>
+        <v>2.366666</v>
       </c>
       <c r="F36" s="9" t="n">
         <v>2.2</v>
@@ -3506,9 +3644,12 @@
       </c>
       <c r="K36" s="9"/>
       <c r="L36" s="9" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M36" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3517,12 +3658,12 @@
         <v>31</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C37" s="8"/>
       <c r="D37" s="8"/>
       <c r="E37" s="7" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="F37" s="9" t="n">
         <v>1.5</v>
@@ -3541,9 +3682,12 @@
       </c>
       <c r="K37" s="9"/>
       <c r="L37" s="9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M37" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3552,12 +3696,12 @@
         <v>32</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C38" s="8"/>
       <c r="D38" s="8"/>
       <c r="E38" s="7" t="n">
-        <v>3.368</v>
+        <v>3.373333</v>
       </c>
       <c r="F38" s="9" t="n">
         <v>3.43</v>
@@ -3576,9 +3720,12 @@
       </c>
       <c r="K38" s="9"/>
       <c r="L38" s="9" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="M38" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3587,12 +3734,12 @@
         <v>33</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C39" s="8"/>
       <c r="D39" s="8"/>
       <c r="E39" s="7" t="n">
-        <v>3.18</v>
+        <v>3.183333</v>
       </c>
       <c r="F39" s="9" t="n">
         <v>3.1</v>
@@ -3611,9 +3758,12 @@
       </c>
       <c r="K39" s="9"/>
       <c r="L39" s="9" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M39" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3622,12 +3772,12 @@
         <v>34</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C40" s="8"/>
       <c r="D40" s="8"/>
       <c r="E40" s="7" t="n">
-        <v>1.78</v>
+        <v>1.766666</v>
       </c>
       <c r="F40" s="9" t="n">
         <v>1.7</v>
@@ -3646,9 +3796,12 @@
       </c>
       <c r="K40" s="9"/>
       <c r="L40" s="9" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M40" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3657,12 +3810,12 @@
         <v>35</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C41" s="8"/>
       <c r="D41" s="8"/>
       <c r="E41" s="7" t="n">
-        <v>0.9</v>
+        <v>0.883333</v>
       </c>
       <c r="F41" s="9" t="n">
         <v>0.9</v>
@@ -3681,9 +3834,12 @@
       </c>
       <c r="K41" s="9"/>
       <c r="L41" s="9" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="M41" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3692,12 +3848,12 @@
         <v>36</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C42" s="8"/>
       <c r="D42" s="8"/>
       <c r="E42" s="7" t="n">
-        <v>0.9</v>
+        <v>0.883333</v>
       </c>
       <c r="F42" s="9" t="n">
         <v>0.9</v>
@@ -3716,9 +3872,12 @@
       </c>
       <c r="K42" s="9"/>
       <c r="L42" s="9" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="M42" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3727,12 +3886,12 @@
         <v>37</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C43" s="8"/>
       <c r="D43" s="8"/>
       <c r="E43" s="7" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="F43" s="9" t="n">
         <v>1.5</v>
@@ -3751,9 +3910,12 @@
       </c>
       <c r="K43" s="9"/>
       <c r="L43" s="9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M43" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3762,12 +3924,12 @@
         <v>38</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C44" s="8"/>
       <c r="D44" s="8"/>
       <c r="E44" s="7" t="n">
-        <v>1.16</v>
+        <v>1.133333</v>
       </c>
       <c r="F44" s="9" t="n">
         <v>1.2</v>
@@ -3786,9 +3948,12 @@
       </c>
       <c r="K44" s="9"/>
       <c r="L44" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M44" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3797,12 +3962,12 @@
         <v>39</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C45" s="8"/>
       <c r="D45" s="8"/>
       <c r="E45" s="7" t="n">
-        <v>0.77</v>
+        <v>0.775</v>
       </c>
       <c r="F45" s="9" t="n">
         <v>0.83</v>
@@ -3821,9 +3986,12 @@
       </c>
       <c r="K45" s="9"/>
       <c r="L45" s="9" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="M45" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3832,12 +4000,12 @@
         <v>40</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C46" s="8"/>
       <c r="D46" s="8"/>
       <c r="E46" s="7" t="n">
-        <v>0.742</v>
+        <v>0.735</v>
       </c>
       <c r="F46" s="9" t="n">
         <v>0.77</v>
@@ -3856,9 +4024,12 @@
       </c>
       <c r="K46" s="9"/>
       <c r="L46" s="9" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="M46" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3867,12 +4038,12 @@
         <v>41</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C47" s="8"/>
       <c r="D47" s="8"/>
       <c r="E47" s="7" t="n">
-        <v>0.73</v>
+        <v>0.725</v>
       </c>
       <c r="F47" s="9" t="n">
         <v>0.76</v>
@@ -3891,9 +4062,12 @@
       </c>
       <c r="K47" s="9"/>
       <c r="L47" s="9" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="M47" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3902,12 +4076,12 @@
         <v>42</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C48" s="8"/>
       <c r="D48" s="8"/>
       <c r="E48" s="7" t="n">
-        <v>0.77</v>
+        <v>0.775</v>
       </c>
       <c r="F48" s="9" t="n">
         <v>0.8</v>
@@ -3926,9 +4100,12 @@
       </c>
       <c r="K48" s="9"/>
       <c r="L48" s="9" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="M48" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3937,7 +4114,7 @@
         <v>43</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C49" s="8"/>
       <c r="D49" s="8"/>
@@ -3961,9 +4138,12 @@
       </c>
       <c r="K49" s="9"/>
       <c r="L49" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M49" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3972,12 +4152,12 @@
         <v>44</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C50" s="8"/>
       <c r="D50" s="8"/>
       <c r="E50" s="7" t="n">
-        <v>0.674</v>
+        <v>0.678333</v>
       </c>
       <c r="F50" s="9" t="n">
         <v>0.7</v>
@@ -3996,9 +4176,12 @@
       </c>
       <c r="K50" s="9"/>
       <c r="L50" s="9" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="M50" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4007,7 +4190,7 @@
         <v>45</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C51" s="8"/>
       <c r="D51" s="8"/>
@@ -4031,9 +4214,12 @@
       </c>
       <c r="K51" s="9"/>
       <c r="L51" s="9" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="M51" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4042,12 +4228,12 @@
         <v>46</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C52" s="8"/>
       <c r="D52" s="8"/>
       <c r="E52" s="7" t="n">
-        <v>1.08</v>
+        <v>1.083333</v>
       </c>
       <c r="F52" s="9" t="n">
         <v>1</v>
@@ -4066,9 +4252,12 @@
       </c>
       <c r="K52" s="9"/>
       <c r="L52" s="9" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="M52" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4077,12 +4266,12 @@
         <v>47</v>
       </c>
       <c r="B53" s="8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C53" s="8"/>
       <c r="D53" s="8"/>
       <c r="E53" s="7" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="F53" s="9" t="n">
         <v>1.5</v>
@@ -4101,9 +4290,12 @@
       </c>
       <c r="K53" s="9"/>
       <c r="L53" s="9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M53" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4112,12 +4304,12 @@
         <v>48</v>
       </c>
       <c r="B54" s="8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C54" s="8"/>
       <c r="D54" s="8"/>
       <c r="E54" s="7" t="n">
-        <v>0.92</v>
+        <v>0.916666</v>
       </c>
       <c r="F54" s="9" t="n">
         <v>0.8</v>
@@ -4136,9 +4328,12 @@
       </c>
       <c r="K54" s="9"/>
       <c r="L54" s="9" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="M54" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4147,12 +4342,12 @@
         <v>49</v>
       </c>
       <c r="B55" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C55" s="8"/>
       <c r="D55" s="8"/>
       <c r="E55" s="7" t="n">
-        <v>1.654</v>
+        <v>1.645</v>
       </c>
       <c r="F55" s="9" t="n">
         <v>1.7</v>
@@ -4171,9 +4366,12 @@
       </c>
       <c r="K55" s="9"/>
       <c r="L55" s="9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M55" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4182,12 +4380,12 @@
         <v>50</v>
       </c>
       <c r="B56" s="8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C56" s="8"/>
       <c r="D56" s="8"/>
       <c r="E56" s="7" t="n">
-        <v>1.16</v>
+        <v>1.133333</v>
       </c>
       <c r="F56" s="9" t="n">
         <v>1.2</v>
@@ -4206,9 +4404,12 @@
       </c>
       <c r="K56" s="9"/>
       <c r="L56" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M56" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4217,12 +4418,12 @@
         <v>51</v>
       </c>
       <c r="B57" s="8" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C57" s="8"/>
       <c r="D57" s="8"/>
       <c r="E57" s="7" t="n">
-        <v>0.732</v>
+        <v>0.743333</v>
       </c>
       <c r="F57" s="9" t="n">
         <v>0.72</v>
@@ -4241,9 +4442,12 @@
       </c>
       <c r="K57" s="9"/>
       <c r="L57" s="9" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="M57" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4252,7 +4456,7 @@
         <v>52</v>
       </c>
       <c r="B58" s="8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C58" s="8"/>
       <c r="D58" s="8"/>
@@ -4276,9 +4480,12 @@
       </c>
       <c r="K58" s="9"/>
       <c r="L58" s="9" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="M58" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4287,7 +4494,7 @@
         <v>53</v>
       </c>
       <c r="B59" s="8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C59" s="8"/>
       <c r="D59" s="8"/>
@@ -4311,9 +4518,12 @@
       </c>
       <c r="K59" s="9"/>
       <c r="L59" s="9" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="M59" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4322,12 +4532,12 @@
         <v>54</v>
       </c>
       <c r="B60" s="8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C60" s="8"/>
       <c r="D60" s="8"/>
       <c r="E60" s="7" t="n">
-        <v>1.14</v>
+        <v>1.116666</v>
       </c>
       <c r="F60" s="9" t="n">
         <v>1.2</v>
@@ -4346,9 +4556,12 @@
       </c>
       <c r="K60" s="9"/>
       <c r="L60" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M60" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4357,12 +4570,12 @@
         <v>55</v>
       </c>
       <c r="B61" s="8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C61" s="8"/>
       <c r="D61" s="8"/>
       <c r="E61" s="7" t="n">
-        <v>0.88</v>
+        <v>0.9</v>
       </c>
       <c r="F61" s="9" t="n">
         <v>0.8</v>
@@ -4381,9 +4594,12 @@
       </c>
       <c r="K61" s="9"/>
       <c r="L61" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M61" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4392,12 +4608,12 @@
         <v>56</v>
       </c>
       <c r="B62" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C62" s="8"/>
       <c r="D62" s="8"/>
       <c r="E62" s="7" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="F62" s="9" t="n">
         <v>0.7</v>
@@ -4416,9 +4632,12 @@
       </c>
       <c r="K62" s="9"/>
       <c r="L62" s="9" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="M62" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4427,12 +4646,12 @@
         <v>57</v>
       </c>
       <c r="B63" s="8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C63" s="8"/>
       <c r="D63" s="8"/>
       <c r="E63" s="7" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="F63" s="9" t="n">
         <v>0.7</v>
@@ -4451,9 +4670,12 @@
       </c>
       <c r="K63" s="9"/>
       <c r="L63" s="9" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="M63" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N63" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4462,12 +4684,12 @@
         <v>58</v>
       </c>
       <c r="B64" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C64" s="8"/>
       <c r="D64" s="8"/>
       <c r="E64" s="7" t="n">
-        <v>1.04</v>
+        <v>1.033333</v>
       </c>
       <c r="F64" s="9" t="n">
         <v>1</v>
@@ -4486,9 +4708,12 @@
       </c>
       <c r="K64" s="9"/>
       <c r="L64" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M64" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N64" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4497,12 +4722,12 @@
         <v>59</v>
       </c>
       <c r="B65" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C65" s="8"/>
       <c r="D65" s="8"/>
       <c r="E65" s="7" t="n">
-        <v>0.82</v>
+        <v>0.833333</v>
       </c>
       <c r="F65" s="9" t="n">
         <v>0.7</v>
@@ -4521,9 +4746,12 @@
       </c>
       <c r="K65" s="9"/>
       <c r="L65" s="9" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="M65" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N65" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4532,12 +4760,12 @@
         <v>60</v>
       </c>
       <c r="B66" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C66" s="8"/>
       <c r="D66" s="8"/>
       <c r="E66" s="7" t="n">
-        <v>2.88</v>
+        <v>2.916666</v>
       </c>
       <c r="F66" s="9" t="n">
         <v>3</v>
@@ -4556,9 +4784,12 @@
       </c>
       <c r="K66" s="9"/>
       <c r="L66" s="9" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="M66" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N66" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4567,12 +4798,12 @@
         <v>61</v>
       </c>
       <c r="B67" s="8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C67" s="8"/>
       <c r="D67" s="8"/>
       <c r="E67" s="7" t="n">
-        <v>1.496</v>
+        <v>1.496666</v>
       </c>
       <c r="F67" s="9" t="n">
         <v>1.4</v>
@@ -4591,9 +4822,12 @@
       </c>
       <c r="K67" s="9"/>
       <c r="L67" s="9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M67" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N67" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4602,12 +4836,12 @@
         <v>62</v>
       </c>
       <c r="B68" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C68" s="8"/>
       <c r="D68" s="8"/>
       <c r="E68" s="7" t="n">
-        <v>2.5</v>
+        <v>2.483333</v>
       </c>
       <c r="F68" s="9" t="n">
         <v>2.5</v>
@@ -4626,9 +4860,12 @@
       </c>
       <c r="K68" s="9"/>
       <c r="L68" s="9" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M68" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N68" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4637,7 +4874,7 @@
         <v>63</v>
       </c>
       <c r="B69" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C69" s="8"/>
       <c r="D69" s="8"/>
@@ -4661,9 +4898,12 @@
       </c>
       <c r="K69" s="9"/>
       <c r="L69" s="9" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M69" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N69" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4672,12 +4912,12 @@
         <v>64</v>
       </c>
       <c r="B70" s="8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C70" s="8"/>
       <c r="D70" s="8"/>
       <c r="E70" s="7" t="n">
-        <v>2.52</v>
+        <v>2.516666</v>
       </c>
       <c r="F70" s="9" t="n">
         <v>2.6</v>
@@ -4696,9 +4936,12 @@
       </c>
       <c r="K70" s="9"/>
       <c r="L70" s="9" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M70" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N70" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4707,7 +4950,7 @@
         <v>65</v>
       </c>
       <c r="B71" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C71" s="8"/>
       <c r="D71" s="8"/>
@@ -4731,9 +4974,12 @@
       </c>
       <c r="K71" s="9"/>
       <c r="L71" s="9" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="M71" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N71" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4742,7 +4988,7 @@
         <v>66</v>
       </c>
       <c r="B72" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C72" s="8"/>
       <c r="D72" s="8"/>
@@ -4766,9 +5012,12 @@
       </c>
       <c r="K72" s="9"/>
       <c r="L72" s="9" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M72" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N72" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4777,12 +5026,12 @@
         <v>67</v>
       </c>
       <c r="B73" s="8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C73" s="8"/>
       <c r="D73" s="8"/>
       <c r="E73" s="7" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="F73" s="9" t="n">
         <v>1.9</v>
@@ -4801,9 +5050,12 @@
       </c>
       <c r="K73" s="9"/>
       <c r="L73" s="9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M73" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N73" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4812,7 +5064,7 @@
         <v>68</v>
       </c>
       <c r="B74" s="8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C74" s="8"/>
       <c r="D74" s="8"/>
@@ -4836,9 +5088,12 @@
       </c>
       <c r="K74" s="9"/>
       <c r="L74" s="9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M74" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N74" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4847,12 +5102,12 @@
         <v>69</v>
       </c>
       <c r="B75" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C75" s="8"/>
       <c r="D75" s="8"/>
       <c r="E75" s="7" t="n">
-        <v>0.834</v>
+        <v>0.845</v>
       </c>
       <c r="F75" s="9" t="n">
         <v>0.92</v>
@@ -4871,9 +5126,12 @@
       </c>
       <c r="K75" s="9"/>
       <c r="L75" s="9" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="M75" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N75" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4882,12 +5140,12 @@
         <v>70</v>
       </c>
       <c r="B76" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C76" s="8"/>
       <c r="D76" s="8"/>
       <c r="E76" s="7" t="n">
-        <v>0.824</v>
+        <v>0.836666</v>
       </c>
       <c r="F76" s="9" t="n">
         <v>0.9</v>
@@ -4906,9 +5164,12 @@
       </c>
       <c r="K76" s="9"/>
       <c r="L76" s="9" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="M76" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N76" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4917,12 +5178,12 @@
         <v>71</v>
       </c>
       <c r="B77" s="8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C77" s="8"/>
       <c r="D77" s="8"/>
       <c r="E77" s="7" t="n">
-        <v>1.06</v>
+        <v>1.083333</v>
       </c>
       <c r="F77" s="9" t="n">
         <v>0.9</v>
@@ -4941,9 +5202,12 @@
       </c>
       <c r="K77" s="9"/>
       <c r="L77" s="9" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="M77" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N77" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4952,12 +5216,12 @@
         <v>72</v>
       </c>
       <c r="B78" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C78" s="8"/>
       <c r="D78" s="8"/>
       <c r="E78" s="7" t="n">
-        <v>0.94</v>
+        <v>0.966666</v>
       </c>
       <c r="F78" s="9" t="n">
         <v>0.7</v>
@@ -4976,9 +5240,12 @@
       </c>
       <c r="K78" s="9"/>
       <c r="L78" s="9" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="M78" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N78" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4987,12 +5254,12 @@
         <v>73</v>
       </c>
       <c r="B79" s="8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C79" s="8"/>
       <c r="D79" s="8"/>
       <c r="E79" s="7" t="n">
-        <v>1.5</v>
+        <v>1.516666</v>
       </c>
       <c r="F79" s="9" t="n">
         <v>1.5</v>
@@ -5011,9 +5278,12 @@
       </c>
       <c r="K79" s="9"/>
       <c r="L79" s="9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M79" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N79" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5022,7 +5292,7 @@
         <v>74</v>
       </c>
       <c r="B80" s="8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C80" s="8"/>
       <c r="D80" s="8"/>
@@ -5046,9 +5316,12 @@
       </c>
       <c r="K80" s="9"/>
       <c r="L80" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M80" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N80" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5057,12 +5330,12 @@
         <v>75</v>
       </c>
       <c r="B81" s="8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C81" s="8"/>
       <c r="D81" s="8"/>
       <c r="E81" s="7" t="n">
-        <v>0.96</v>
+        <v>0.983333</v>
       </c>
       <c r="F81" s="9" t="n">
         <v>0.8</v>
@@ -5081,9 +5354,12 @@
       </c>
       <c r="K81" s="9"/>
       <c r="L81" s="9" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="M81" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N81" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5092,12 +5368,12 @@
         <v>76</v>
       </c>
       <c r="B82" s="8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C82" s="8"/>
       <c r="D82" s="8"/>
       <c r="E82" s="7" t="n">
-        <v>0.8</v>
+        <v>0.816666</v>
       </c>
       <c r="F82" s="9" t="n">
         <v>0.8</v>
@@ -5116,9 +5392,12 @@
       </c>
       <c r="K82" s="9"/>
       <c r="L82" s="9" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="M82" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N82" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5127,12 +5406,12 @@
         <v>77</v>
       </c>
       <c r="B83" s="8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C83" s="8"/>
       <c r="D83" s="8"/>
       <c r="E83" s="7" t="n">
-        <v>5.4</v>
+        <v>5.433333</v>
       </c>
       <c r="F83" s="9" t="n">
         <v>5.4</v>
@@ -5151,9 +5430,12 @@
       </c>
       <c r="K83" s="9"/>
       <c r="L83" s="9" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="M83" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N83" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5162,12 +5444,12 @@
         <v>78</v>
       </c>
       <c r="B84" s="8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C84" s="8"/>
       <c r="D84" s="8"/>
       <c r="E84" s="7" t="n">
-        <v>1.84</v>
+        <v>1.833333</v>
       </c>
       <c r="F84" s="9" t="n">
         <v>1.84</v>
@@ -5186,9 +5468,12 @@
       </c>
       <c r="K84" s="9"/>
       <c r="L84" s="9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M84" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N84" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5197,7 +5482,7 @@
         <v>79</v>
       </c>
       <c r="B85" s="8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C85" s="8"/>
       <c r="D85" s="8"/>
@@ -5221,9 +5506,12 @@
       </c>
       <c r="K85" s="9"/>
       <c r="L85" s="9" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M85" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N85" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5232,12 +5520,12 @@
         <v>80</v>
       </c>
       <c r="B86" s="8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C86" s="8"/>
       <c r="D86" s="8"/>
       <c r="E86" s="7" t="n">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="F86" s="9" t="n">
         <v>1.1</v>
@@ -5256,9 +5544,12 @@
       </c>
       <c r="K86" s="9"/>
       <c r="L86" s="9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M86" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N86" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5267,12 +5558,12 @@
         <v>81</v>
       </c>
       <c r="B87" s="8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C87" s="8"/>
       <c r="D87" s="8"/>
       <c r="E87" s="7" t="n">
-        <v>1.6</v>
+        <v>1.583333</v>
       </c>
       <c r="F87" s="9" t="n">
         <v>1.6</v>
@@ -5291,9 +5582,12 @@
       </c>
       <c r="K87" s="9"/>
       <c r="L87" s="9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M87" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N87" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5302,12 +5596,12 @@
         <v>82</v>
       </c>
       <c r="B88" s="8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C88" s="8"/>
       <c r="D88" s="8"/>
       <c r="E88" s="7" t="n">
-        <v>1.8</v>
+        <v>1.816666</v>
       </c>
       <c r="F88" s="9" t="n">
         <v>1.8</v>
@@ -5326,9 +5620,12 @@
       </c>
       <c r="K88" s="9"/>
       <c r="L88" s="9" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M88" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N88" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5337,7 +5634,7 @@
         <v>83</v>
       </c>
       <c r="B89" s="8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C89" s="8"/>
       <c r="D89" s="8"/>
@@ -5361,9 +5658,12 @@
       </c>
       <c r="K89" s="9"/>
       <c r="L89" s="9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M89" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N89" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5372,12 +5672,12 @@
         <v>84</v>
       </c>
       <c r="B90" s="8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C90" s="8"/>
       <c r="D90" s="8"/>
       <c r="E90" s="7" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="F90" s="9" t="n">
         <v>1.9</v>
@@ -5396,9 +5696,12 @@
       </c>
       <c r="K90" s="9"/>
       <c r="L90" s="9" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M90" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N90" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5407,7 +5710,7 @@
         <v>85</v>
       </c>
       <c r="B91" s="8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C91" s="8"/>
       <c r="D91" s="8"/>
@@ -5431,9 +5734,12 @@
       </c>
       <c r="K91" s="9"/>
       <c r="L91" s="9" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="M91" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N91" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5442,12 +5748,12 @@
         <v>86</v>
       </c>
       <c r="B92" s="8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C92" s="8"/>
       <c r="D92" s="8"/>
       <c r="E92" s="7" t="n">
-        <v>1.72</v>
+        <v>1.716666</v>
       </c>
       <c r="F92" s="9" t="n">
         <v>1.8</v>
@@ -5466,9 +5772,12 @@
       </c>
       <c r="K92" s="9"/>
       <c r="L92" s="9" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M92" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N92" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5477,7 +5786,7 @@
         <v>87</v>
       </c>
       <c r="B93" s="8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C93" s="8"/>
       <c r="D93" s="8"/>
@@ -5501,9 +5810,12 @@
       </c>
       <c r="K93" s="9"/>
       <c r="L93" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M93" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N93" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5512,12 +5824,12 @@
         <v>88</v>
       </c>
       <c r="B94" s="8" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C94" s="8"/>
       <c r="D94" s="8"/>
       <c r="E94" s="7" t="n">
-        <v>2.44</v>
+        <v>2.433333</v>
       </c>
       <c r="F94" s="9" t="n">
         <v>2.6</v>
@@ -5536,9 +5848,12 @@
       </c>
       <c r="K94" s="9"/>
       <c r="L94" s="9" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M94" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N94" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5547,12 +5862,12 @@
         <v>89</v>
       </c>
       <c r="B95" s="8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C95" s="8"/>
       <c r="D95" s="8"/>
       <c r="E95" s="7" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="F95" s="9" t="n">
         <v>1.7</v>
@@ -5571,9 +5886,12 @@
       </c>
       <c r="K95" s="9"/>
       <c r="L95" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M95" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N95" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5582,12 +5900,12 @@
         <v>90</v>
       </c>
       <c r="B96" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C96" s="8"/>
       <c r="D96" s="8"/>
       <c r="E96" s="7" t="n">
-        <v>1.02</v>
+        <v>1.033333</v>
       </c>
       <c r="F96" s="9" t="n">
         <v>1.1</v>
@@ -5606,9 +5924,12 @@
       </c>
       <c r="K96" s="9"/>
       <c r="L96" s="9" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="M96" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N96" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5617,12 +5938,12 @@
         <v>91</v>
       </c>
       <c r="B97" s="8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C97" s="8"/>
       <c r="D97" s="8"/>
       <c r="E97" s="7" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="F97" s="9" t="n">
         <v>2.2</v>
@@ -5641,9 +5962,12 @@
       </c>
       <c r="K97" s="9"/>
       <c r="L97" s="9" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M97" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N97" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5652,12 +5976,12 @@
         <v>92</v>
       </c>
       <c r="B98" s="8" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C98" s="8"/>
       <c r="D98" s="8"/>
       <c r="E98" s="7" t="n">
-        <v>1.58</v>
+        <v>1.583333</v>
       </c>
       <c r="F98" s="9" t="n">
         <v>1.5</v>
@@ -5676,9 +6000,12 @@
       </c>
       <c r="K98" s="9"/>
       <c r="L98" s="9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M98" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N98" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5687,12 +6014,12 @@
         <v>93</v>
       </c>
       <c r="B99" s="8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C99" s="8"/>
       <c r="D99" s="8"/>
       <c r="E99" s="7" t="n">
-        <v>2</v>
+        <v>2.016666</v>
       </c>
       <c r="F99" s="9" t="n">
         <v>2</v>
@@ -5711,9 +6038,12 @@
       </c>
       <c r="K99" s="9"/>
       <c r="L99" s="9" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M99" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N99" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5722,7 +6052,7 @@
         <v>94</v>
       </c>
       <c r="B100" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C100" s="8"/>
       <c r="D100" s="8"/>
@@ -5746,9 +6076,12 @@
       </c>
       <c r="K100" s="9"/>
       <c r="L100" s="9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M100" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N100" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5757,12 +6090,12 @@
         <v>95</v>
       </c>
       <c r="B101" s="8" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C101" s="8"/>
       <c r="D101" s="8"/>
       <c r="E101" s="7" t="n">
-        <v>0.58</v>
+        <v>0.583333</v>
       </c>
       <c r="F101" s="9" t="n">
         <v>0.5</v>
@@ -5781,9 +6114,12 @@
       </c>
       <c r="K101" s="9"/>
       <c r="L101" s="9" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="M101" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N101" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5792,12 +6128,12 @@
         <v>96</v>
       </c>
       <c r="B102" s="8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C102" s="8"/>
       <c r="D102" s="8"/>
       <c r="E102" s="7" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="F102" s="9" t="n">
         <v>0.5</v>
@@ -5816,9 +6152,12 @@
       </c>
       <c r="K102" s="9"/>
       <c r="L102" s="9" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="M102" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N102" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5827,12 +6166,12 @@
         <v>97</v>
       </c>
       <c r="B103" s="8" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C103" s="8"/>
       <c r="D103" s="8"/>
       <c r="E103" s="7" t="n">
-        <v>0.78</v>
+        <v>0.783333</v>
       </c>
       <c r="F103" s="9" t="n">
         <v>0.7</v>
@@ -5851,9 +6190,12 @@
       </c>
       <c r="K103" s="9"/>
       <c r="L103" s="9" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="M103" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N103" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5862,12 +6204,12 @@
         <v>98</v>
       </c>
       <c r="B104" s="8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C104" s="8"/>
       <c r="D104" s="8"/>
       <c r="E104" s="7" t="n">
-        <v>0.96</v>
+        <v>0.966666</v>
       </c>
       <c r="F104" s="9" t="n">
         <v>1</v>
@@ -5886,9 +6228,12 @@
       </c>
       <c r="K104" s="9"/>
       <c r="L104" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M104" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N104" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5897,12 +6242,12 @@
         <v>99</v>
       </c>
       <c r="B105" s="8" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C105" s="8"/>
       <c r="D105" s="8"/>
       <c r="E105" s="7" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="F105" s="9" t="n">
         <v>1.2</v>
@@ -5921,9 +6266,12 @@
       </c>
       <c r="K105" s="9"/>
       <c r="L105" s="9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M105" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N105" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5932,12 +6280,12 @@
         <v>100</v>
       </c>
       <c r="B106" s="8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C106" s="8"/>
       <c r="D106" s="8"/>
       <c r="E106" s="7" t="n">
-        <v>1.3</v>
+        <v>1.316666</v>
       </c>
       <c r="F106" s="9" t="n">
         <v>1.3</v>
@@ -5956,9 +6304,12 @@
       </c>
       <c r="K106" s="9"/>
       <c r="L106" s="9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M106" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N106" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5985,10 +6336,11 @@
       <c r="T107" s="10"/>
       <c r="U107" s="10"/>
       <c r="V107" s="10"/>
+      <c r="W107" s="10"/>
     </row>
     <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="11" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B108" s="11"/>
       <c r="C108" s="11"/>
@@ -6000,7 +6352,7 @@
       <c r="I108" s="11"/>
       <c r="J108" s="11"/>
       <c r="K108" s="11" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="L108" s="11"/>
       <c r="M108" s="11"/>
@@ -6013,10 +6365,11 @@
       <c r="T108" s="11"/>
       <c r="U108" s="11"/>
       <c r="V108" s="11"/>
+      <c r="W108" s="11"/>
     </row>
     <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B109" s="11"/>
       <c r="C109" s="11"/>
@@ -6028,7 +6381,7 @@
       <c r="I109" s="11"/>
       <c r="J109" s="11"/>
       <c r="K109" s="11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="L109" s="11"/>
       <c r="M109" s="11"/>
@@ -6041,10 +6394,11 @@
       <c r="T109" s="11"/>
       <c r="U109" s="11"/>
       <c r="V109" s="11"/>
+      <c r="W109" s="11"/>
     </row>
     <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="12" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B110" s="12"/>
       <c r="C110" s="12"/>
@@ -6056,7 +6410,7 @@
       <c r="I110" s="12"/>
       <c r="J110" s="12"/>
       <c r="K110" s="12" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L110" s="12"/>
       <c r="M110" s="12"/>
@@ -6069,6 +6423,7 @@
       <c r="T110" s="12"/>
       <c r="U110" s="12"/>
       <c r="V110" s="12"/>
+      <c r="W110" s="12"/>
     </row>
     <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="13"/>
@@ -6082,39 +6437,40 @@
       <c r="I111" s="10"/>
       <c r="J111" s="10"/>
       <c r="K111" s="13" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L111" s="13"/>
       <c r="M111" s="13"/>
       <c r="N111" s="13"/>
-      <c r="O111" s="14" t="s">
-        <v>118</v>
-      </c>
-      <c r="P111" s="13" t="s">
+      <c r="O111" s="13"/>
+      <c r="P111" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="Q111" s="13"/>
-      <c r="R111" s="15" t="s">
+      <c r="Q111" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="S111" s="12" t="s">
+      <c r="R111" s="13"/>
+      <c r="S111" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="T111" s="14" t="s">
-        <v>120</v>
-      </c>
-      <c r="U111" s="10"/>
+      <c r="T111" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="U111" s="14" t="s">
+        <v>121</v>
+      </c>
       <c r="V111" s="10"/>
+      <c r="W111" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="226">
     <mergeCell ref="A1:B3"/>
-    <mergeCell ref="C1:P1"/>
-    <mergeCell ref="Q1:U1"/>
-    <mergeCell ref="C2:P2"/>
-    <mergeCell ref="Q2:U2"/>
-    <mergeCell ref="C3:P3"/>
-    <mergeCell ref="Q3:U3"/>
+    <mergeCell ref="C1:Q1"/>
+    <mergeCell ref="R1:V1"/>
+    <mergeCell ref="C2:Q2"/>
+    <mergeCell ref="R2:V2"/>
+    <mergeCell ref="C3:Q3"/>
+    <mergeCell ref="R3:V3"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="J4:K4"/>
     <mergeCell ref="B5:D5"/>
@@ -6322,18 +6678,18 @@
     <mergeCell ref="B106:D106"/>
     <mergeCell ref="J106:K106"/>
     <mergeCell ref="A107:J107"/>
-    <mergeCell ref="K107:V107"/>
+    <mergeCell ref="K107:W107"/>
     <mergeCell ref="A108:J108"/>
-    <mergeCell ref="K108:V108"/>
+    <mergeCell ref="K108:W108"/>
     <mergeCell ref="A109:J109"/>
-    <mergeCell ref="K109:V109"/>
+    <mergeCell ref="K109:W109"/>
     <mergeCell ref="A110:J110"/>
-    <mergeCell ref="K110:V110"/>
+    <mergeCell ref="K110:W110"/>
     <mergeCell ref="A111:C111"/>
     <mergeCell ref="D111:J111"/>
-    <mergeCell ref="K111:N111"/>
-    <mergeCell ref="P111:Q111"/>
-    <mergeCell ref="U111:V111"/>
+    <mergeCell ref="K111:O111"/>
+    <mergeCell ref="Q111:R111"/>
+    <mergeCell ref="V111:W111"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
